--- a/artfynd/A 22906-2021 artfynd.xlsx
+++ b/artfynd/A 22906-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121259576</v>
+        <v>121259573</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>90717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612879</v>
+        <v>612902</v>
       </c>
       <c r="R2" t="n">
-        <v>6553805</v>
+        <v>6553814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>121259581</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121259573</v>
+        <v>121259576</v>
       </c>
       <c r="B4" t="n">
-        <v>90707</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612902</v>
+        <v>612879</v>
       </c>
       <c r="R4" t="n">
-        <v>6553814</v>
+        <v>6553805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22906-2021 artfynd.xlsx
+++ b/artfynd/A 22906-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121259573</v>
+        <v>121259576</v>
       </c>
       <c r="B2" t="n">
-        <v>90717</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612902</v>
+        <v>612879</v>
       </c>
       <c r="R2" t="n">
-        <v>6553814</v>
+        <v>6553805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121259581</v>
+        <v>121259573</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>90717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Solbacka, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612811</v>
+        <v>612902</v>
       </c>
       <c r="R3" t="n">
-        <v>6553817</v>
+        <v>6553814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121259576</v>
+        <v>121259581</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,34 +895,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Solbacka, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612879</v>
+        <v>612811</v>
       </c>
       <c r="R4" t="n">
-        <v>6553805</v>
+        <v>6553817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22906-2021 artfynd.xlsx
+++ b/artfynd/A 22906-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121259576</v>
+        <v>121259573</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>90729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612879</v>
+        <v>612902</v>
       </c>
       <c r="R2" t="n">
-        <v>6553805</v>
+        <v>6553814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121259573</v>
+        <v>121259581</v>
       </c>
       <c r="B3" t="n">
-        <v>90717</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Solbacka, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612902</v>
+        <v>612811</v>
       </c>
       <c r="R3" t="n">
-        <v>6553814</v>
+        <v>6553817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121259581</v>
+        <v>121259576</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,43 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Solbacka, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612811</v>
+        <v>612879</v>
       </c>
       <c r="R4" t="n">
-        <v>6553817</v>
+        <v>6553805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22906-2021 artfynd.xlsx
+++ b/artfynd/A 22906-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121259573</v>
+        <v>121259576</v>
       </c>
       <c r="B2" t="n">
-        <v>90729</v>
+        <v>100361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612902</v>
+        <v>612879</v>
       </c>
       <c r="R2" t="n">
-        <v>6553814</v>
+        <v>6553805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121259581</v>
+        <v>121259573</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>90730</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Solbacka, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612811</v>
+        <v>612902</v>
       </c>
       <c r="R3" t="n">
-        <v>6553817</v>
+        <v>6553814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121259576</v>
+        <v>121259581</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,34 +895,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Solbacka, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612879</v>
+        <v>612811</v>
       </c>
       <c r="R4" t="n">
-        <v>6553805</v>
+        <v>6553817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22906-2021 artfynd.xlsx
+++ b/artfynd/A 22906-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121259576</v>
+        <v>121259573</v>
       </c>
       <c r="B2" t="n">
-        <v>100361</v>
+        <v>90733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612879</v>
+        <v>612902</v>
       </c>
       <c r="R2" t="n">
-        <v>6553805</v>
+        <v>6553814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121259573</v>
+        <v>121259576</v>
       </c>
       <c r="B3" t="n">
-        <v>90730</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612902</v>
+        <v>612879</v>
       </c>
       <c r="R3" t="n">
-        <v>6553814</v>
+        <v>6553805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>121259581</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 22906-2021 artfynd.xlsx
+++ b/artfynd/A 22906-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121259573</v>
       </c>
       <c r="B2" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121259576</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121259581</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 22906-2021 artfynd.xlsx
+++ b/artfynd/A 22906-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121259573</v>
+        <v>121259576</v>
       </c>
       <c r="B2" t="n">
-        <v>90739</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612902</v>
+        <v>612879</v>
       </c>
       <c r="R2" t="n">
-        <v>6553814</v>
+        <v>6553805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121259576</v>
+        <v>121259573</v>
       </c>
       <c r="B3" t="n">
-        <v>100370</v>
+        <v>90740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612879</v>
+        <v>612902</v>
       </c>
       <c r="R3" t="n">
-        <v>6553805</v>
+        <v>6553814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>121259581</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 22906-2021 artfynd.xlsx
+++ b/artfynd/A 22906-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121259576</v>
+        <v>121259573</v>
       </c>
       <c r="B2" t="n">
-        <v>100371</v>
+        <v>90740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612879</v>
+        <v>612902</v>
       </c>
       <c r="R2" t="n">
-        <v>6553805</v>
+        <v>6553814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121259573</v>
+        <v>121259581</v>
       </c>
       <c r="B3" t="n">
-        <v>90740</v>
+        <v>57375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Solbacka, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612902</v>
+        <v>612811</v>
       </c>
       <c r="R3" t="n">
-        <v>6553814</v>
+        <v>6553817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121259581</v>
+        <v>121259576</v>
       </c>
       <c r="B4" t="n">
-        <v>57375</v>
+        <v>100371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,43 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Solbacka, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612811</v>
+        <v>612879</v>
       </c>
       <c r="R4" t="n">
-        <v>6553817</v>
+        <v>6553805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
